--- a/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
+++ b/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\assignments\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D216712B-82CB-45FA-8CD5-31EA3A1444CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4EEBB0-90E3-438D-A4E9-DB436D85186C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="25035" windowHeight="10635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="555" yWindow="705" windowWidth="28020" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="54">
   <si>
     <t>بريد المعلم</t>
   </si>
@@ -53,9 +53,6 @@
     <t>حالة الإسناد</t>
   </si>
   <si>
-    <t>a.aljidawii@qz.org.sa</t>
-  </si>
-  <si>
     <t>mrb-boys-sayh</t>
   </si>
   <si>
@@ -68,18 +65,6 @@
     <t>ACTIVE</t>
   </si>
   <si>
-    <t>a.attab@qz.org.sa</t>
-  </si>
-  <si>
-    <t>m.bayoumi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>aa.alamer@qz.org.sa</t>
-  </si>
-  <si>
-    <t>t.altawala@qz.org.sa</t>
-  </si>
-  <si>
     <t>الحقل</t>
   </si>
   <si>
@@ -120,13 +105,91 @@
   </si>
   <si>
     <t>كل صف يمثل إسناد مادة واحدة لمعلم داخل فصل واحد.</t>
+  </si>
+  <si>
+    <t>a.h.almasoud@qz.org.sa</t>
+  </si>
+  <si>
+    <t>g4-general-1</t>
+  </si>
+  <si>
+    <t>رابع عام</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g4-general-1-math</t>
+  </si>
+  <si>
+    <t>MATH</t>
+  </si>
+  <si>
+    <t>رياضيات</t>
+  </si>
+  <si>
+    <t>DIGITAL</t>
+  </si>
+  <si>
+    <t>رقمية</t>
+  </si>
+  <si>
+    <t>g4-quran-1</t>
+  </si>
+  <si>
+    <t>رابع تحفيظ</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g4-quran-1-math</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g4-quran-1-art</t>
+  </si>
+  <si>
+    <t>ART</t>
+  </si>
+  <si>
+    <t>فنية</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g4-quran-1-digital</t>
+  </si>
+  <si>
+    <t>g5-general-1</t>
+  </si>
+  <si>
+    <t>خامس</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g5-general-1-math</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g5-general-1-pe</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>بدنية</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g5-general-1-digital</t>
+  </si>
+  <si>
+    <t>g6-general-1</t>
+  </si>
+  <si>
+    <t>سادس</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g6-general-1-digital</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g4-general-1-digital</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -135,6 +198,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -168,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -182,6 +253,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -200,7 +272,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAssignmentsImportTable" displayName="TeacherAssignmentsImportTable" ref="A1:J6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAssignmentsImportTable" displayName="TeacherAssignmentsImportTable" ref="A1:J10">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="بريد المعلم"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="معرّف المدرسة"/>
@@ -366,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -379,7 +451,7 @@
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1">
+    <row r="1" spans="1:10" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,119 +483,298 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.1" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" ht="16.5">
+      <c r="A2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.1" customHeight="1">
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="26.1" customHeight="1">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="26.1" customHeight="1">
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="26.1" customHeight="1">
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="J2:J100" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="J2:J104" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"ACTIVE,INACTIVE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -545,10 +796,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="36" customHeight="1">
@@ -556,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="36" customHeight="1">
@@ -564,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="36" customHeight="1">
@@ -572,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="36" customHeight="1">
@@ -580,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="36" customHeight="1">
@@ -588,7 +839,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="36" customHeight="1">
@@ -596,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="36" customHeight="1">
@@ -604,7 +855,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="36" customHeight="1">
@@ -612,7 +863,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="36" customHeight="1">
@@ -620,7 +871,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="36" customHeight="1">
@@ -628,15 +879,15 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="36" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
+++ b/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\assignments\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A7C1D2-2C4F-410B-902D-C3286B4496D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A303A7B-0FF8-491F-8CC9-2E9E6AC5BF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="2340" windowWidth="28680" windowHeight="12090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12465" yWindow="3360" windowWidth="14355" windowHeight="8190" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="455">
   <si>
     <t>بريد المعلم</t>
   </si>
@@ -1363,6 +1363,30 @@
   </si>
   <si>
     <t>mrb-girls-g6-quran-1-science</t>
+  </si>
+  <si>
+    <t>w-a-atwala@qz.org.sa</t>
+  </si>
+  <si>
+    <t>mrb-girls-g5-quran-2-tajweed</t>
+  </si>
+  <si>
+    <t>r-g-alfraj@qz.org.sa</t>
+  </si>
+  <si>
+    <t>mrb-girls-g3-quran-2-science</t>
+  </si>
+  <si>
+    <t>mrb-girls-g4-quran-2-science</t>
+  </si>
+  <si>
+    <t>n-r-arbya@qz.org.sa</t>
+  </si>
+  <si>
+    <t>mrb-girls-g4-quran-2-digital</t>
+  </si>
+  <si>
+    <t>mrb-girls-g5-quran-2-digital</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J307"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -1742,10 +1766,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>447</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -1754,19 +1778,19 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>316</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>317</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>448</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -1774,1527 +1798,130 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>449</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G3" t="s">
+        <v>450</v>
+      </c>
+      <c r="H3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>449</v>
+      </c>
+      <c r="B4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G4" t="s">
+        <v>451</v>
+      </c>
+      <c r="H4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>452</v>
+      </c>
+      <c r="B5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" t="s">
+        <v>334</v>
+      </c>
+      <c r="G5" t="s">
+        <v>453</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1">
-      <c r="A203" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1">
-      <c r="A215" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1">
-      <c r="A230" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1">
-      <c r="A245" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1">
-      <c r="A248" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1">
-      <c r="A249" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1">
-      <c r="A250" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1">
-      <c r="A251" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1">
-      <c r="A252" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1">
-      <c r="A253" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1">
-      <c r="A255" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1">
-      <c r="A258" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1">
-      <c r="A259" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1">
-      <c r="A260" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1">
-      <c r="A261" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1">
-      <c r="A262" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1">
-      <c r="A263" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1">
-      <c r="A264" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1">
-      <c r="A265" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1">
-      <c r="A266" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1">
-      <c r="A267" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1">
-      <c r="A268" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1">
-      <c r="A269" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1">
-      <c r="A271" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1">
-      <c r="A272" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1">
-      <c r="A273" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1">
-      <c r="A274" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1">
-      <c r="A275" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1">
-      <c r="A276" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1">
-      <c r="A277" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1">
-      <c r="A278" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1">
-      <c r="A279" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1">
-      <c r="A280" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1">
-      <c r="A281" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1">
-      <c r="A282" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1">
-      <c r="A283" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1">
-      <c r="A284" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1">
-      <c r="A285" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1">
-      <c r="A286" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1">
-      <c r="A287" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1">
-      <c r="A288" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1">
-      <c r="A289" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1">
-      <c r="A290" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1">
-      <c r="A291" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1">
-      <c r="A292" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1">
-      <c r="A293" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1">
-      <c r="A294" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1">
-      <c r="A295" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1">
-      <c r="A296" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1">
-      <c r="A297" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1">
-      <c r="A298" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1">
-      <c r="A299" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1">
-      <c r="A300" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1">
-      <c r="A301" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1">
-      <c r="A302" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1">
-      <c r="A303" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1">
-      <c r="A304" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1">
-      <c r="A305" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1">
-      <c r="A306" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1">
-      <c r="A307" t="s">
-        <v>439</v>
+        <v>452</v>
+      </c>
+      <c r="B6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G6" t="s">
+        <v>454</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
+++ b/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\assignments\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDAF3FA-C0D8-474D-B48C-28EF1AAF2D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA2A39B-7624-4954-8E64-91321654C4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="105" windowWidth="19980" windowHeight="15405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
     <sheet name="التوزيع (الفالح)" sheetId="4" r:id="rId2"/>
     <sheet name="تعليمات" sheetId="2" r:id="rId3"/>
     <sheet name="نسخة من التوزيع" sheetId="3" r:id="rId4"/>
+    <sheet name="التوزيع (2)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="282">
   <si>
     <t>الحقل</t>
   </si>
@@ -857,6 +858,18 @@
   </si>
   <si>
     <t xml:space="preserve">ثاني ابتدائي / عام </t>
+  </si>
+  <si>
+    <t>g2-quran-1</t>
+  </si>
+  <si>
+    <t>ثاني ابتدائي / تحفيظ</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g2-quran-1-art</t>
+  </si>
+  <si>
+    <t>mrb-boys-sayh-g2-quran-1-arabic</t>
   </si>
 </sst>
 </file>
@@ -875,7 +888,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -902,6 +915,12 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -915,7 +934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -944,6 +963,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,7 +982,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAssignmentsImportTable" displayName="TeacherAssignmentsImportTable" ref="A1:J307">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAssignmentsImportTable" displayName="TeacherAssignmentsImportTable" ref="A1:J211">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="بريد المعلم"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="معرّف المدرسة"/>
@@ -1010,6 +1030,24 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="رمز المادة"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="اسم المادة للتوضيح"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="حالة الإسناد"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D49BE05C-90B1-42A0-B5E7-D768F1CDAAC0}" name="TeacherAssignmentsImportTable5" displayName="TeacherAssignmentsImportTable5" ref="A1:J307">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{2D3F7724-E3BE-4AC8-9EAF-33DD236D8A8A}" name="بريد المعلم"/>
+    <tableColumn id="2" xr3:uid="{1D31EE44-1725-42BB-A376-1A357608AD43}" name="معرّف المدرسة"/>
+    <tableColumn id="3" xr3:uid="{6A9D5672-BE14-4D6A-A47D-39E621B45D06}" name="معرّف السنة الدراسية"/>
+    <tableColumn id="4" xr3:uid="{401C3C68-2D2D-41F5-A0F9-7AAF22106FBC}" name="معرّف الفصل الدراسي"/>
+    <tableColumn id="5" xr3:uid="{193660C9-D7F1-4950-89EB-7EDDCEAF36CB}" name="معرّف الفصل"/>
+    <tableColumn id="6" xr3:uid="{26900889-152E-4405-99F5-27CC9A5E9384}" name="اسم الفصل للتوضيح"/>
+    <tableColumn id="7" xr3:uid="{AD5EB321-5F06-423F-95FB-2A18F4A60CE9}" name="معرّف إسناد المادة"/>
+    <tableColumn id="8" xr3:uid="{7FC6B7DA-7B16-47CE-A12D-C95F4E0620AA}" name="رمز المادة"/>
+    <tableColumn id="9" xr3:uid="{7864AC0A-702E-482A-82B7-1655C4AB03F0}" name="اسم المادة للتوضيح"/>
+    <tableColumn id="10" xr3:uid="{03448F16-1473-4E58-AAEB-8D94378B4DC8}" name="حالة الإسناد"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1164,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -1210,3209 +1248,137 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" t="s">
-        <v>264</v>
-      </c>
-      <c r="G4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
+    <row r="2" spans="1:10" s="10" customFormat="1">
+      <c r="A2" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F2" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="G7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="G2" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" t="s">
-        <v>265</v>
-      </c>
-      <c r="G9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="J2" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1">
+      <c r="A3" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="10" customFormat="1">
+      <c r="A4" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>144</v>
-      </c>
-      <c r="G10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" t="s">
-        <v>277</v>
-      </c>
-      <c r="G11" t="s">
-        <v>161</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G13" t="s">
-        <v>162</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A14" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F14" t="s">
-        <v>275</v>
-      </c>
-      <c r="G14" t="s">
-        <v>164</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" t="s">
-        <v>274</v>
-      </c>
-      <c r="G15" t="s">
-        <v>166</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B16" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>167</v>
-      </c>
-      <c r="F16" t="s">
-        <v>272</v>
-      </c>
-      <c r="G16" t="s">
-        <v>168</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" t="s">
-        <v>165</v>
-      </c>
-      <c r="B17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" t="s">
-        <v>266</v>
-      </c>
-      <c r="G17" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" t="s">
-        <v>266</v>
-      </c>
-      <c r="G18" t="s">
-        <v>170</v>
-      </c>
-      <c r="H18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" t="s">
-        <v>265</v>
-      </c>
-      <c r="G19" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A20" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" t="s">
-        <v>264</v>
-      </c>
-      <c r="G20" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20" t="s">
-        <v>89</v>
-      </c>
-      <c r="J20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A21" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I21" t="s">
-        <v>89</v>
-      </c>
-      <c r="J21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A22" t="s">
-        <v>172</v>
-      </c>
-      <c r="B22" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" t="s">
-        <v>147</v>
-      </c>
-      <c r="G22" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I22" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A23" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F23" t="s">
-        <v>272</v>
-      </c>
-      <c r="G23" t="s">
-        <v>176</v>
-      </c>
-      <c r="H23" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" t="s">
-        <v>266</v>
-      </c>
-      <c r="G24" t="s">
-        <v>177</v>
-      </c>
-      <c r="H24" t="s">
-        <v>75</v>
-      </c>
-      <c r="I24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A25" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" t="s">
-        <v>265</v>
-      </c>
-      <c r="G25" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" t="s">
-        <v>75</v>
-      </c>
-      <c r="I25" t="s">
-        <v>76</v>
-      </c>
-      <c r="J25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A26" t="s">
-        <v>179</v>
-      </c>
-      <c r="B26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" t="s">
-        <v>263</v>
-      </c>
-      <c r="G26" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26" t="s">
-        <v>89</v>
-      </c>
-      <c r="J26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A27" t="s">
-        <v>179</v>
-      </c>
-      <c r="B27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" t="s">
-        <v>145</v>
-      </c>
-      <c r="G28" t="s">
-        <v>182</v>
-      </c>
-      <c r="H28" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28" t="s">
-        <v>89</v>
-      </c>
-      <c r="J28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A29" t="s">
-        <v>179</v>
-      </c>
-      <c r="B29" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" t="s">
-        <v>273</v>
-      </c>
-      <c r="G29" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29" t="s">
-        <v>89</v>
-      </c>
-      <c r="J29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A30" t="s">
-        <v>184</v>
-      </c>
-      <c r="B30" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" t="s">
-        <v>144</v>
-      </c>
-      <c r="G30" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I30" t="s">
-        <v>89</v>
-      </c>
-      <c r="J30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" t="s">
-        <v>144</v>
-      </c>
-      <c r="G31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" t="s">
-        <v>89</v>
-      </c>
-      <c r="J31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A32" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" t="s">
-        <v>266</v>
-      </c>
-      <c r="G32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32" t="s">
-        <v>89</v>
-      </c>
-      <c r="J32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A33" t="s">
-        <v>184</v>
-      </c>
-      <c r="B33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" t="s">
-        <v>266</v>
-      </c>
-      <c r="G33" t="s">
-        <v>187</v>
-      </c>
-      <c r="H33" t="s">
-        <v>125</v>
-      </c>
-      <c r="I33" t="s">
-        <v>126</v>
-      </c>
-      <c r="J33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A34" t="s">
-        <v>188</v>
-      </c>
-      <c r="B34" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" t="s">
-        <v>147</v>
-      </c>
-      <c r="G34" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A35" t="s">
-        <v>188</v>
-      </c>
-      <c r="B35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s">
-        <v>54</v>
-      </c>
-      <c r="F35" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" t="s">
-        <v>190</v>
-      </c>
-      <c r="H35" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A36" t="s">
-        <v>188</v>
-      </c>
-      <c r="B36" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" t="s">
-        <v>167</v>
-      </c>
-      <c r="F36" t="s">
-        <v>272</v>
-      </c>
-      <c r="G36" t="s">
-        <v>191</v>
-      </c>
-      <c r="H36" t="s">
-        <v>88</v>
-      </c>
-      <c r="I36" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A37" t="s">
-        <v>188</v>
-      </c>
-      <c r="B37" t="s">
-        <v>150</v>
-      </c>
-      <c r="C37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" t="s">
-        <v>265</v>
-      </c>
-      <c r="G37" t="s">
-        <v>192</v>
-      </c>
-      <c r="H37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I37" t="s">
-        <v>89</v>
-      </c>
-      <c r="J37" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A38" t="s">
-        <v>193</v>
-      </c>
-      <c r="B38" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" t="s">
-        <v>144</v>
-      </c>
-      <c r="G38" t="s">
-        <v>194</v>
-      </c>
-      <c r="H38" t="s">
-        <v>112</v>
-      </c>
-      <c r="I38" t="s">
-        <v>113</v>
-      </c>
-      <c r="J38" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A39" t="s">
-        <v>193</v>
-      </c>
-      <c r="B39" t="s">
-        <v>150</v>
-      </c>
-      <c r="C39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" t="s">
-        <v>195</v>
-      </c>
-      <c r="H39" t="s">
-        <v>112</v>
-      </c>
-      <c r="I39" t="s">
-        <v>113</v>
-      </c>
-      <c r="J39" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A40" t="s">
-        <v>193</v>
-      </c>
-      <c r="B40" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F40" t="s">
-        <v>273</v>
-      </c>
-      <c r="G40" t="s">
-        <v>196</v>
-      </c>
-      <c r="H40" t="s">
-        <v>112</v>
-      </c>
-      <c r="I40" t="s">
-        <v>113</v>
-      </c>
-      <c r="J40" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B41" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" t="s">
-        <v>63</v>
-      </c>
-      <c r="F41" t="s">
-        <v>265</v>
-      </c>
-      <c r="G41" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41" t="s">
-        <v>112</v>
-      </c>
-      <c r="I41" t="s">
-        <v>113</v>
-      </c>
-      <c r="J41" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A42" t="s">
-        <v>198</v>
-      </c>
-      <c r="B42" t="s">
-        <v>150</v>
-      </c>
-      <c r="C42" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" t="s">
-        <v>263</v>
-      </c>
-      <c r="G42" t="s">
-        <v>199</v>
-      </c>
-      <c r="H42" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A43" t="s">
-        <v>198</v>
-      </c>
-      <c r="B43" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" t="s">
-        <v>24</v>
-      </c>
-      <c r="F43" t="s">
-        <v>263</v>
-      </c>
-      <c r="G43" t="s">
-        <v>200</v>
-      </c>
-      <c r="H43" t="s">
-        <v>112</v>
-      </c>
-      <c r="I43" t="s">
-        <v>113</v>
-      </c>
-      <c r="J43" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A44" t="s">
-        <v>198</v>
-      </c>
-      <c r="B44" t="s">
-        <v>150</v>
-      </c>
-      <c r="C44" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" t="s">
-        <v>153</v>
-      </c>
-      <c r="F44" t="s">
-        <v>264</v>
-      </c>
-      <c r="G44" t="s">
-        <v>201</v>
-      </c>
-      <c r="H44" t="s">
-        <v>112</v>
-      </c>
-      <c r="I44" t="s">
-        <v>113</v>
-      </c>
-      <c r="J44" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A45" t="s">
-        <v>198</v>
-      </c>
-      <c r="B45" t="s">
-        <v>150</v>
-      </c>
-      <c r="C45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G45" t="s">
-        <v>202</v>
-      </c>
-      <c r="H45" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" t="s">
-        <v>35</v>
-      </c>
-      <c r="J45" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A46" t="s">
-        <v>198</v>
-      </c>
-      <c r="B46" t="s">
-        <v>150</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" t="s">
-        <v>36</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G46" t="s">
-        <v>203</v>
-      </c>
-      <c r="H46" t="s">
-        <v>112</v>
-      </c>
-      <c r="I46" t="s">
-        <v>113</v>
-      </c>
-      <c r="J46" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A47" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" t="s">
-        <v>144</v>
-      </c>
-      <c r="G47" t="s">
-        <v>194</v>
-      </c>
-      <c r="H47" t="s">
-        <v>112</v>
-      </c>
-      <c r="I47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J47" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A48" t="s">
-        <v>198</v>
-      </c>
-      <c r="B48" t="s">
-        <v>150</v>
-      </c>
-      <c r="C48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" t="s">
-        <v>167</v>
-      </c>
-      <c r="F48" t="s">
-        <v>272</v>
-      </c>
-      <c r="G48" t="s">
-        <v>204</v>
-      </c>
-      <c r="H48" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A49" t="s">
-        <v>205</v>
-      </c>
-      <c r="B49" t="s">
-        <v>150</v>
-      </c>
-      <c r="C49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" t="s">
-        <v>163</v>
-      </c>
-      <c r="F49" t="s">
-        <v>273</v>
-      </c>
-      <c r="G49" t="s">
-        <v>206</v>
-      </c>
-      <c r="H49" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" t="s">
-        <v>35</v>
-      </c>
-      <c r="J49" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A50" t="s">
-        <v>205</v>
-      </c>
-      <c r="B50" t="s">
-        <v>150</v>
-      </c>
-      <c r="C50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" t="s">
-        <v>147</v>
-      </c>
-      <c r="G50" t="s">
-        <v>207</v>
-      </c>
-      <c r="H50" t="s">
-        <v>112</v>
-      </c>
-      <c r="I50" t="s">
-        <v>113</v>
-      </c>
-      <c r="J50" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A51" t="s">
-        <v>205</v>
-      </c>
-      <c r="B51" t="s">
-        <v>150</v>
-      </c>
-      <c r="C51" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" t="s">
-        <v>54</v>
-      </c>
-      <c r="F51" t="s">
-        <v>147</v>
-      </c>
-      <c r="G51" t="s">
-        <v>208</v>
-      </c>
-      <c r="H51" t="s">
-        <v>51</v>
-      </c>
-      <c r="I51" t="s">
-        <v>52</v>
-      </c>
-      <c r="J51" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A52" t="s">
-        <v>205</v>
-      </c>
-      <c r="B52" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" t="s">
-        <v>167</v>
-      </c>
-      <c r="F52" t="s">
-        <v>272</v>
-      </c>
-      <c r="G52" t="s">
-        <v>209</v>
-      </c>
-      <c r="H52" t="s">
-        <v>112</v>
-      </c>
-      <c r="I52" t="s">
-        <v>113</v>
-      </c>
-      <c r="J52" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A53" t="s">
-        <v>205</v>
-      </c>
-      <c r="B53" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" t="s">
-        <v>167</v>
-      </c>
-      <c r="F53" t="s">
-        <v>272</v>
-      </c>
-      <c r="G53" t="s">
-        <v>210</v>
-      </c>
-      <c r="H53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I53" t="s">
-        <v>52</v>
-      </c>
-      <c r="J53" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A54" t="s">
-        <v>205</v>
-      </c>
-      <c r="B54" t="s">
-        <v>150</v>
-      </c>
-      <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" t="s">
-        <v>47</v>
-      </c>
-      <c r="F54" t="s">
-        <v>266</v>
-      </c>
-      <c r="G54" t="s">
-        <v>211</v>
-      </c>
-      <c r="H54" t="s">
-        <v>112</v>
-      </c>
-      <c r="I54" t="s">
-        <v>113</v>
-      </c>
-      <c r="J54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A55" t="s">
-        <v>205</v>
-      </c>
-      <c r="B55" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" t="s">
-        <v>47</v>
-      </c>
-      <c r="F55" t="s">
-        <v>266</v>
-      </c>
-      <c r="G55" t="s">
-        <v>212</v>
-      </c>
-      <c r="H55" t="s">
-        <v>51</v>
-      </c>
-      <c r="I55" t="s">
-        <v>52</v>
-      </c>
-      <c r="J55" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A56" t="s">
-        <v>205</v>
-      </c>
-      <c r="B56" t="s">
-        <v>150</v>
-      </c>
-      <c r="C56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" t="s">
-        <v>63</v>
-      </c>
-      <c r="F56" t="s">
-        <v>265</v>
-      </c>
-      <c r="G56" t="s">
-        <v>213</v>
-      </c>
-      <c r="H56" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56" t="s">
-        <v>52</v>
-      </c>
-      <c r="J56" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A57" t="s">
-        <v>214</v>
-      </c>
-      <c r="B57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" t="s">
-        <v>54</v>
-      </c>
-      <c r="F57" t="s">
-        <v>147</v>
-      </c>
-      <c r="G57" t="s">
-        <v>215</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="J4" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1">
+      <c r="A5" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I5" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J57" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A58" t="s">
-        <v>214</v>
-      </c>
-      <c r="B58" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" t="s">
-        <v>167</v>
-      </c>
-      <c r="F58" t="s">
-        <v>272</v>
-      </c>
-      <c r="G58" t="s">
-        <v>216</v>
-      </c>
-      <c r="H58" t="s">
-        <v>82</v>
-      </c>
-      <c r="I58" t="s">
-        <v>83</v>
-      </c>
-      <c r="J58" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A59" t="s">
-        <v>214</v>
-      </c>
-      <c r="B59" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" t="s">
-        <v>47</v>
-      </c>
-      <c r="F59" t="s">
-        <v>266</v>
-      </c>
-      <c r="G59" t="s">
-        <v>217</v>
-      </c>
-      <c r="H59" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59" t="s">
-        <v>32</v>
-      </c>
-      <c r="J59" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A60" t="s">
-        <v>214</v>
-      </c>
-      <c r="B60" t="s">
-        <v>150</v>
-      </c>
-      <c r="C60" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" t="s">
-        <v>47</v>
-      </c>
-      <c r="F60" t="s">
-        <v>266</v>
-      </c>
-      <c r="G60" t="s">
-        <v>218</v>
-      </c>
-      <c r="H60" t="s">
-        <v>82</v>
-      </c>
-      <c r="I60" t="s">
-        <v>83</v>
-      </c>
-      <c r="J60" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A61" t="s">
-        <v>214</v>
-      </c>
-      <c r="B61" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" t="s">
-        <v>265</v>
-      </c>
-      <c r="G61" t="s">
-        <v>219</v>
-      </c>
-      <c r="H61" t="s">
-        <v>34</v>
-      </c>
-      <c r="I61" t="s">
-        <v>35</v>
-      </c>
-      <c r="J61" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A62" t="s">
-        <v>214</v>
-      </c>
-      <c r="B62" t="s">
-        <v>150</v>
-      </c>
-      <c r="C62" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" t="s">
-        <v>265</v>
-      </c>
-      <c r="G62" t="s">
-        <v>220</v>
-      </c>
-      <c r="H62" t="s">
-        <v>82</v>
-      </c>
-      <c r="I62" t="s">
-        <v>83</v>
-      </c>
-      <c r="J62" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A63" t="s">
-        <v>221</v>
-      </c>
-      <c r="B63" t="s">
-        <v>150</v>
-      </c>
-      <c r="C63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" t="s">
-        <v>263</v>
-      </c>
-      <c r="G63" t="s">
-        <v>222</v>
-      </c>
-      <c r="H63" t="s">
-        <v>82</v>
-      </c>
-      <c r="I63" t="s">
-        <v>83</v>
-      </c>
-      <c r="J63" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B64" t="s">
-        <v>150</v>
-      </c>
-      <c r="C64" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" t="s">
-        <v>153</v>
-      </c>
-      <c r="F64" t="s">
-        <v>264</v>
-      </c>
-      <c r="G64" t="s">
-        <v>224</v>
-      </c>
-      <c r="H64" t="s">
-        <v>82</v>
-      </c>
-      <c r="I64" t="s">
-        <v>83</v>
-      </c>
-      <c r="J64" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A65" t="s">
-        <v>223</v>
-      </c>
-      <c r="B65" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" t="s">
-        <v>22</v>
-      </c>
-      <c r="D65" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G65" t="s">
-        <v>225</v>
-      </c>
-      <c r="H65" t="s">
-        <v>82</v>
-      </c>
-      <c r="I65" t="s">
-        <v>83</v>
-      </c>
-      <c r="J65" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A66" t="s">
-        <v>226</v>
-      </c>
-      <c r="B66" t="s">
-        <v>150</v>
-      </c>
-      <c r="C66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" t="s">
-        <v>43</v>
-      </c>
-      <c r="F66" t="s">
-        <v>145</v>
-      </c>
-      <c r="G66" t="s">
-        <v>227</v>
-      </c>
-      <c r="H66" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J66" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>226</v>
-      </c>
-      <c r="B67" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67" t="s">
-        <v>145</v>
-      </c>
-      <c r="G67" t="s">
-        <v>228</v>
-      </c>
-      <c r="H67" t="s">
-        <v>82</v>
-      </c>
-      <c r="I67" t="s">
-        <v>83</v>
-      </c>
-      <c r="J67" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>226</v>
-      </c>
-      <c r="B68" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" t="s">
-        <v>163</v>
-      </c>
-      <c r="F68" t="s">
-        <v>273</v>
-      </c>
-      <c r="G68" t="s">
-        <v>229</v>
-      </c>
-      <c r="H68" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" t="s">
-        <v>32</v>
-      </c>
-      <c r="J68" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" t="s">
-        <v>226</v>
-      </c>
-      <c r="B69" t="s">
-        <v>150</v>
-      </c>
-      <c r="C69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" t="s">
-        <v>163</v>
-      </c>
-      <c r="F69" t="s">
-        <v>273</v>
-      </c>
-      <c r="G69" t="s">
-        <v>230</v>
-      </c>
-      <c r="H69" t="s">
-        <v>82</v>
-      </c>
-      <c r="I69" t="s">
-        <v>83</v>
-      </c>
-      <c r="J69" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>226</v>
-      </c>
-      <c r="B70" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" t="s">
-        <v>167</v>
-      </c>
-      <c r="F70" t="s">
-        <v>272</v>
-      </c>
-      <c r="G70" t="s">
-        <v>231</v>
-      </c>
-      <c r="H70" t="s">
-        <v>125</v>
-      </c>
-      <c r="I70" t="s">
-        <v>126</v>
-      </c>
-      <c r="J70" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>226</v>
-      </c>
-      <c r="B71" t="s">
-        <v>150</v>
-      </c>
-      <c r="C71" t="s">
-        <v>22</v>
-      </c>
-      <c r="D71" t="s">
-        <v>23</v>
-      </c>
-      <c r="E71" t="s">
-        <v>63</v>
-      </c>
-      <c r="F71" t="s">
-        <v>271</v>
-      </c>
-      <c r="G71" t="s">
-        <v>232</v>
-      </c>
-      <c r="H71" t="s">
-        <v>125</v>
-      </c>
-      <c r="I71" t="s">
-        <v>126</v>
-      </c>
-      <c r="J71" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" t="s">
-        <v>233</v>
-      </c>
-      <c r="B72" t="s">
-        <v>150</v>
-      </c>
-      <c r="C72" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" t="s">
-        <v>40</v>
-      </c>
-      <c r="F72" t="s">
-        <v>144</v>
-      </c>
-      <c r="G72" t="s">
-        <v>234</v>
-      </c>
-      <c r="H72" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" t="s">
-        <v>32</v>
-      </c>
-      <c r="J72" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" t="s">
-        <v>233</v>
-      </c>
-      <c r="B73" t="s">
-        <v>150</v>
-      </c>
-      <c r="C73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" t="s">
-        <v>23</v>
-      </c>
-      <c r="E73" t="s">
-        <v>40</v>
-      </c>
-      <c r="F73" t="s">
-        <v>144</v>
-      </c>
-      <c r="G73" t="s">
-        <v>235</v>
-      </c>
-      <c r="H73" t="s">
-        <v>82</v>
-      </c>
-      <c r="I73" t="s">
-        <v>83</v>
-      </c>
-      <c r="J73" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" t="s">
-        <v>233</v>
-      </c>
-      <c r="B74" t="s">
-        <v>150</v>
-      </c>
-      <c r="C74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" t="s">
-        <v>40</v>
-      </c>
-      <c r="F74" t="s">
-        <v>144</v>
-      </c>
-      <c r="G74" t="s">
-        <v>234</v>
-      </c>
-      <c r="H74" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" t="s">
-        <v>32</v>
-      </c>
-      <c r="J74" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" t="s">
-        <v>233</v>
-      </c>
-      <c r="B75" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" t="s">
-        <v>22</v>
-      </c>
-      <c r="D75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" t="s">
-        <v>40</v>
-      </c>
-      <c r="F75" t="s">
-        <v>144</v>
-      </c>
-      <c r="G75" t="s">
-        <v>235</v>
-      </c>
-      <c r="H75" t="s">
-        <v>82</v>
-      </c>
-      <c r="I75" t="s">
-        <v>83</v>
-      </c>
-      <c r="J75" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" t="s">
-        <v>236</v>
-      </c>
-      <c r="B76" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" t="s">
-        <v>24</v>
-      </c>
-      <c r="F76" t="s">
-        <v>263</v>
-      </c>
-      <c r="G76" t="s">
-        <v>237</v>
-      </c>
-      <c r="H76" t="s">
-        <v>70</v>
-      </c>
-      <c r="I76" t="s">
-        <v>71</v>
-      </c>
-      <c r="J76" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
-      <c r="A77" t="s">
-        <v>236</v>
-      </c>
-      <c r="B77" t="s">
-        <v>150</v>
-      </c>
-      <c r="C77" t="s">
-        <v>22</v>
-      </c>
-      <c r="D77" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" t="s">
-        <v>153</v>
-      </c>
-      <c r="F77" t="s">
-        <v>264</v>
-      </c>
-      <c r="G77" t="s">
-        <v>238</v>
-      </c>
-      <c r="H77" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" t="s">
-        <v>32</v>
-      </c>
-      <c r="J77" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" t="s">
-        <v>236</v>
-      </c>
-      <c r="B78" t="s">
-        <v>150</v>
-      </c>
-      <c r="C78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" t="s">
-        <v>153</v>
-      </c>
-      <c r="F78" t="s">
-        <v>264</v>
-      </c>
-      <c r="G78" t="s">
-        <v>239</v>
-      </c>
-      <c r="H78" t="s">
-        <v>70</v>
-      </c>
-      <c r="I78" t="s">
-        <v>71</v>
-      </c>
-      <c r="J78" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" t="s">
-        <v>236</v>
-      </c>
-      <c r="B79" t="s">
-        <v>150</v>
-      </c>
-      <c r="C79" t="s">
-        <v>22</v>
-      </c>
-      <c r="D79" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" t="s">
-        <v>36</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G79" t="s">
-        <v>240</v>
-      </c>
-      <c r="H79" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" t="s">
-        <v>32</v>
-      </c>
-      <c r="J79" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" t="s">
-        <v>236</v>
-      </c>
-      <c r="B80" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" t="s">
-        <v>23</v>
-      </c>
-      <c r="E80" t="s">
-        <v>36</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G80" t="s">
-        <v>241</v>
-      </c>
-      <c r="H80" t="s">
-        <v>70</v>
-      </c>
-      <c r="I80" t="s">
-        <v>71</v>
-      </c>
-      <c r="J80" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" t="s">
-        <v>236</v>
-      </c>
-      <c r="B81" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81" t="s">
-        <v>23</v>
-      </c>
-      <c r="E81" t="s">
-        <v>40</v>
-      </c>
-      <c r="F81" t="s">
-        <v>144</v>
-      </c>
-      <c r="G81" t="s">
-        <v>242</v>
-      </c>
-      <c r="H81" t="s">
-        <v>70</v>
-      </c>
-      <c r="I81" t="s">
-        <v>71</v>
-      </c>
-      <c r="J81" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" t="s">
-        <v>236</v>
-      </c>
-      <c r="B82" t="s">
-        <v>150</v>
-      </c>
-      <c r="C82" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" t="s">
-        <v>23</v>
-      </c>
-      <c r="E82" t="s">
-        <v>40</v>
-      </c>
-      <c r="F82" t="s">
-        <v>144</v>
-      </c>
-      <c r="G82" t="s">
-        <v>242</v>
-      </c>
-      <c r="H82" t="s">
-        <v>70</v>
-      </c>
-      <c r="I82" t="s">
-        <v>71</v>
-      </c>
-      <c r="J82" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" t="s">
-        <v>236</v>
-      </c>
-      <c r="B83" t="s">
-        <v>150</v>
-      </c>
-      <c r="C83" t="s">
-        <v>22</v>
-      </c>
-      <c r="D83" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" t="s">
-        <v>63</v>
-      </c>
-      <c r="F83" t="s">
-        <v>271</v>
-      </c>
-      <c r="G83" t="s">
-        <v>243</v>
-      </c>
-      <c r="H83" t="s">
-        <v>70</v>
-      </c>
-      <c r="I83" t="s">
-        <v>71</v>
-      </c>
-      <c r="J83" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" t="s">
-        <v>244</v>
-      </c>
-      <c r="B84" t="s">
-        <v>150</v>
-      </c>
-      <c r="C84" t="s">
-        <v>22</v>
-      </c>
-      <c r="D84" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" t="s">
-        <v>43</v>
-      </c>
-      <c r="F84" t="s">
-        <v>145</v>
-      </c>
-      <c r="G84" t="s">
-        <v>245</v>
-      </c>
-      <c r="H84" t="s">
-        <v>70</v>
-      </c>
-      <c r="I84" t="s">
-        <v>71</v>
-      </c>
-      <c r="J84" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" t="s">
-        <v>244</v>
-      </c>
-      <c r="B85" t="s">
-        <v>150</v>
-      </c>
-      <c r="C85" t="s">
-        <v>22</v>
-      </c>
-      <c r="D85" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" t="s">
-        <v>163</v>
-      </c>
-      <c r="F85" t="s">
-        <v>273</v>
-      </c>
-      <c r="G85" t="s">
-        <v>246</v>
-      </c>
-      <c r="H85" t="s">
-        <v>70</v>
-      </c>
-      <c r="I85" t="s">
-        <v>71</v>
-      </c>
-      <c r="J85" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" t="s">
-        <v>244</v>
-      </c>
-      <c r="B86" t="s">
-        <v>150</v>
-      </c>
-      <c r="C86" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" t="s">
-        <v>54</v>
-      </c>
-      <c r="F86" t="s">
-        <v>147</v>
-      </c>
-      <c r="G86" t="s">
-        <v>247</v>
-      </c>
-      <c r="H86" t="s">
-        <v>34</v>
-      </c>
-      <c r="I86" t="s">
-        <v>35</v>
-      </c>
-      <c r="J86" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" t="s">
-        <v>244</v>
-      </c>
-      <c r="B87" t="s">
-        <v>150</v>
-      </c>
-      <c r="C87" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" t="s">
-        <v>54</v>
-      </c>
-      <c r="F87" t="s">
-        <v>147</v>
-      </c>
-      <c r="G87" t="s">
-        <v>248</v>
-      </c>
-      <c r="H87" t="s">
-        <v>70</v>
-      </c>
-      <c r="I87" t="s">
-        <v>71</v>
-      </c>
-      <c r="J87" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="A88" t="s">
-        <v>244</v>
-      </c>
-      <c r="B88" t="s">
-        <v>150</v>
-      </c>
-      <c r="C88" t="s">
-        <v>22</v>
-      </c>
-      <c r="D88" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" t="s">
-        <v>167</v>
-      </c>
-      <c r="F88" t="s">
-        <v>272</v>
-      </c>
-      <c r="G88" t="s">
-        <v>249</v>
-      </c>
-      <c r="H88" t="s">
-        <v>34</v>
-      </c>
-      <c r="I88" t="s">
-        <v>35</v>
-      </c>
-      <c r="J88" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" t="s">
-        <v>244</v>
-      </c>
-      <c r="B89" t="s">
-        <v>150</v>
-      </c>
-      <c r="C89" t="s">
-        <v>22</v>
-      </c>
-      <c r="D89" t="s">
-        <v>23</v>
-      </c>
-      <c r="E89" t="s">
-        <v>167</v>
-      </c>
-      <c r="F89" t="s">
-        <v>272</v>
-      </c>
-      <c r="G89" t="s">
-        <v>250</v>
-      </c>
-      <c r="H89" t="s">
-        <v>70</v>
-      </c>
-      <c r="I89" t="s">
-        <v>71</v>
-      </c>
-      <c r="J89" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" t="s">
-        <v>244</v>
-      </c>
-      <c r="B90" t="s">
-        <v>150</v>
-      </c>
-      <c r="C90" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" t="s">
-        <v>23</v>
-      </c>
-      <c r="E90" t="s">
-        <v>47</v>
-      </c>
-      <c r="F90" t="s">
-        <v>270</v>
-      </c>
-      <c r="G90" t="s">
-        <v>251</v>
-      </c>
-      <c r="H90" t="s">
-        <v>70</v>
-      </c>
-      <c r="I90" t="s">
-        <v>71</v>
-      </c>
-      <c r="J90" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" t="s">
-        <v>252</v>
-      </c>
-      <c r="B91" t="s">
-        <v>150</v>
-      </c>
-      <c r="C91" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91" t="s">
-        <v>23</v>
-      </c>
-      <c r="E91" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" t="s">
-        <v>263</v>
-      </c>
-      <c r="G91" t="s">
-        <v>253</v>
-      </c>
-      <c r="H91" t="s">
-        <v>61</v>
-      </c>
-      <c r="I91" t="s">
-        <v>62</v>
-      </c>
-      <c r="J91" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" t="s">
-        <v>252</v>
-      </c>
-      <c r="B92" t="s">
-        <v>150</v>
-      </c>
-      <c r="C92" t="s">
-        <v>22</v>
-      </c>
-      <c r="D92" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" t="s">
-        <v>153</v>
-      </c>
-      <c r="F92" t="s">
-        <v>264</v>
-      </c>
-      <c r="G92" t="s">
-        <v>254</v>
-      </c>
-      <c r="H92" t="s">
-        <v>61</v>
-      </c>
-      <c r="I92" t="s">
-        <v>62</v>
-      </c>
-      <c r="J92" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>252</v>
-      </c>
-      <c r="B93" t="s">
-        <v>150</v>
-      </c>
-      <c r="C93" t="s">
-        <v>22</v>
-      </c>
-      <c r="D93" t="s">
-        <v>23</v>
-      </c>
-      <c r="E93" t="s">
-        <v>36</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G93" t="s">
-        <v>255</v>
-      </c>
-      <c r="H93" t="s">
-        <v>61</v>
-      </c>
-      <c r="I93" t="s">
-        <v>62</v>
-      </c>
-      <c r="J93" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="A94" t="s">
-        <v>252</v>
-      </c>
-      <c r="B94" t="s">
-        <v>150</v>
-      </c>
-      <c r="C94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D94" t="s">
-        <v>23</v>
-      </c>
-      <c r="E94" t="s">
-        <v>40</v>
-      </c>
-      <c r="F94" t="s">
-        <v>144</v>
-      </c>
-      <c r="G94" t="s">
-        <v>256</v>
-      </c>
-      <c r="H94" t="s">
-        <v>61</v>
-      </c>
-      <c r="I94" t="s">
-        <v>62</v>
-      </c>
-      <c r="J94" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" t="s">
-        <v>252</v>
-      </c>
-      <c r="B95" t="s">
-        <v>150</v>
-      </c>
-      <c r="C95" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95" t="s">
-        <v>23</v>
-      </c>
-      <c r="E95" t="s">
-        <v>40</v>
-      </c>
-      <c r="F95" t="s">
-        <v>267</v>
-      </c>
-      <c r="G95" t="s">
-        <v>256</v>
-      </c>
-      <c r="H95" t="s">
-        <v>61</v>
-      </c>
-      <c r="I95" t="s">
-        <v>62</v>
-      </c>
-      <c r="J95" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" t="s">
-        <v>252</v>
-      </c>
-      <c r="B96" t="s">
-        <v>150</v>
-      </c>
-      <c r="C96" t="s">
-        <v>22</v>
-      </c>
-      <c r="D96" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" t="s">
-        <v>43</v>
-      </c>
-      <c r="F96" t="s">
-        <v>145</v>
-      </c>
-      <c r="G96" t="s">
-        <v>257</v>
-      </c>
-      <c r="H96" t="s">
-        <v>61</v>
-      </c>
-      <c r="I96" t="s">
-        <v>62</v>
-      </c>
-      <c r="J96" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
-      <c r="A97" t="s">
-        <v>252</v>
-      </c>
-      <c r="B97" t="s">
-        <v>150</v>
-      </c>
-      <c r="C97" t="s">
-        <v>22</v>
-      </c>
-      <c r="D97" t="s">
-        <v>23</v>
-      </c>
-      <c r="E97" t="s">
-        <v>163</v>
-      </c>
-      <c r="F97" t="s">
-        <v>273</v>
-      </c>
-      <c r="G97" t="s">
-        <v>258</v>
-      </c>
-      <c r="H97" t="s">
-        <v>61</v>
-      </c>
-      <c r="I97" t="s">
-        <v>62</v>
-      </c>
-      <c r="J97" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" t="s">
-        <v>252</v>
-      </c>
-      <c r="B98" t="s">
-        <v>150</v>
-      </c>
-      <c r="C98" t="s">
-        <v>22</v>
-      </c>
-      <c r="D98" t="s">
-        <v>23</v>
-      </c>
-      <c r="E98" t="s">
-        <v>54</v>
-      </c>
-      <c r="F98" t="s">
-        <v>147</v>
-      </c>
-      <c r="G98" t="s">
-        <v>259</v>
-      </c>
-      <c r="H98" t="s">
-        <v>61</v>
-      </c>
-      <c r="I98" t="s">
-        <v>62</v>
-      </c>
-      <c r="J98" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
-      <c r="A99" t="s">
-        <v>252</v>
-      </c>
-      <c r="B99" t="s">
-        <v>150</v>
-      </c>
-      <c r="C99" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" t="s">
-        <v>23</v>
-      </c>
-      <c r="E99" t="s">
-        <v>167</v>
-      </c>
-      <c r="F99" t="s">
-        <v>272</v>
-      </c>
-      <c r="G99" t="s">
-        <v>260</v>
-      </c>
-      <c r="H99" t="s">
-        <v>61</v>
-      </c>
-      <c r="I99" t="s">
-        <v>62</v>
-      </c>
-      <c r="J99" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" t="s">
-        <v>252</v>
-      </c>
-      <c r="B100" t="s">
-        <v>150</v>
-      </c>
-      <c r="C100" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" t="s">
-        <v>23</v>
-      </c>
-      <c r="E100" t="s">
-        <v>47</v>
-      </c>
-      <c r="F100" t="s">
-        <v>268</v>
-      </c>
-      <c r="G100" t="s">
-        <v>261</v>
-      </c>
-      <c r="H100" t="s">
-        <v>61</v>
-      </c>
-      <c r="I100" t="s">
-        <v>62</v>
-      </c>
-      <c r="J100" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" t="s">
-        <v>252</v>
-      </c>
-      <c r="B101" t="s">
-        <v>150</v>
-      </c>
-      <c r="C101" t="s">
-        <v>22</v>
-      </c>
-      <c r="D101" t="s">
-        <v>23</v>
-      </c>
-      <c r="E101" t="s">
-        <v>63</v>
-      </c>
-      <c r="F101" t="s">
-        <v>269</v>
-      </c>
-      <c r="G101" t="s">
-        <v>262</v>
-      </c>
-      <c r="H101" t="s">
-        <v>61</v>
-      </c>
-      <c r="I101" t="s">
-        <v>62</v>
-      </c>
-      <c r="J101" t="s">
+      <c r="J5" s="10" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="J2:J401" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="J2:J305" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"ACTIVE,INACTIVE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8813,4 +5779,3265 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029718D0-2D8E-4FBD-8D78-A36ECF33734C}">
+  <dimension ref="A1:J101"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="7" width="39" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="27.95" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s">
+        <v>265</v>
+      </c>
+      <c r="G9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>277</v>
+      </c>
+      <c r="G11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>276</v>
+      </c>
+      <c r="G13" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" t="s">
+        <v>275</v>
+      </c>
+      <c r="G14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>274</v>
+      </c>
+      <c r="G15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" t="s">
+        <v>272</v>
+      </c>
+      <c r="G16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>266</v>
+      </c>
+      <c r="G17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" t="s">
+        <v>265</v>
+      </c>
+      <c r="G19" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" t="s">
+        <v>264</v>
+      </c>
+      <c r="G20" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A22" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A23" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" t="s">
+        <v>272</v>
+      </c>
+      <c r="G23" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A25" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" t="s">
+        <v>263</v>
+      </c>
+      <c r="G26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" t="s">
+        <v>181</v>
+      </c>
+      <c r="H27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" t="s">
+        <v>89</v>
+      </c>
+      <c r="J28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" t="s">
+        <v>273</v>
+      </c>
+      <c r="G29" t="s">
+        <v>183</v>
+      </c>
+      <c r="H29" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A30" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" t="s">
+        <v>88</v>
+      </c>
+      <c r="I31" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I32" t="s">
+        <v>89</v>
+      </c>
+      <c r="J32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" t="s">
+        <v>187</v>
+      </c>
+      <c r="H33" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" t="s">
+        <v>126</v>
+      </c>
+      <c r="J33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A34" t="s">
+        <v>188</v>
+      </c>
+      <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" t="s">
+        <v>125</v>
+      </c>
+      <c r="I35" t="s">
+        <v>126</v>
+      </c>
+      <c r="J35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" t="s">
+        <v>272</v>
+      </c>
+      <c r="G36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H36" t="s">
+        <v>88</v>
+      </c>
+      <c r="I36" t="s">
+        <v>89</v>
+      </c>
+      <c r="J36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A37" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" t="s">
+        <v>265</v>
+      </c>
+      <c r="G37" t="s">
+        <v>192</v>
+      </c>
+      <c r="H37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I37" t="s">
+        <v>89</v>
+      </c>
+      <c r="J37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A38" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>144</v>
+      </c>
+      <c r="G38" t="s">
+        <v>194</v>
+      </c>
+      <c r="H38" t="s">
+        <v>112</v>
+      </c>
+      <c r="I38" t="s">
+        <v>113</v>
+      </c>
+      <c r="J38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A39" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" t="s">
+        <v>195</v>
+      </c>
+      <c r="H39" t="s">
+        <v>112</v>
+      </c>
+      <c r="I39" t="s">
+        <v>113</v>
+      </c>
+      <c r="J39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A40" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F40" t="s">
+        <v>273</v>
+      </c>
+      <c r="G40" t="s">
+        <v>196</v>
+      </c>
+      <c r="H40" t="s">
+        <v>112</v>
+      </c>
+      <c r="I40" t="s">
+        <v>113</v>
+      </c>
+      <c r="J40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A41" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" t="s">
+        <v>265</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41" t="s">
+        <v>112</v>
+      </c>
+      <c r="I41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J41" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A42" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
+        <v>263</v>
+      </c>
+      <c r="G42" t="s">
+        <v>199</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" t="s">
+        <v>263</v>
+      </c>
+      <c r="G43" t="s">
+        <v>200</v>
+      </c>
+      <c r="H43" t="s">
+        <v>112</v>
+      </c>
+      <c r="I43" t="s">
+        <v>113</v>
+      </c>
+      <c r="J43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A44" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>153</v>
+      </c>
+      <c r="F44" t="s">
+        <v>264</v>
+      </c>
+      <c r="G44" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44" t="s">
+        <v>112</v>
+      </c>
+      <c r="I44" t="s">
+        <v>113</v>
+      </c>
+      <c r="J44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G45" t="s">
+        <v>202</v>
+      </c>
+      <c r="H45" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A46" t="s">
+        <v>198</v>
+      </c>
+      <c r="B46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G46" t="s">
+        <v>203</v>
+      </c>
+      <c r="H46" t="s">
+        <v>112</v>
+      </c>
+      <c r="I46" t="s">
+        <v>113</v>
+      </c>
+      <c r="J46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" t="s">
+        <v>194</v>
+      </c>
+      <c r="H47" t="s">
+        <v>112</v>
+      </c>
+      <c r="I47" t="s">
+        <v>113</v>
+      </c>
+      <c r="J47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" t="s">
+        <v>167</v>
+      </c>
+      <c r="F48" t="s">
+        <v>272</v>
+      </c>
+      <c r="G48" t="s">
+        <v>204</v>
+      </c>
+      <c r="H48" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" t="s">
+        <v>273</v>
+      </c>
+      <c r="G49" t="s">
+        <v>206</v>
+      </c>
+      <c r="H49" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" t="s">
+        <v>147</v>
+      </c>
+      <c r="G50" t="s">
+        <v>207</v>
+      </c>
+      <c r="H50" t="s">
+        <v>112</v>
+      </c>
+      <c r="I50" t="s">
+        <v>113</v>
+      </c>
+      <c r="J50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A51" t="s">
+        <v>205</v>
+      </c>
+      <c r="B51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" t="s">
+        <v>208</v>
+      </c>
+      <c r="H51" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51" t="s">
+        <v>52</v>
+      </c>
+      <c r="J51" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A52" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" t="s">
+        <v>272</v>
+      </c>
+      <c r="G52" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" t="s">
+        <v>112</v>
+      </c>
+      <c r="I52" t="s">
+        <v>113</v>
+      </c>
+      <c r="J52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A53" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" t="s">
+        <v>167</v>
+      </c>
+      <c r="F53" t="s">
+        <v>272</v>
+      </c>
+      <c r="G53" t="s">
+        <v>210</v>
+      </c>
+      <c r="H53" t="s">
+        <v>51</v>
+      </c>
+      <c r="I53" t="s">
+        <v>52</v>
+      </c>
+      <c r="J53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A54" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" t="s">
+        <v>266</v>
+      </c>
+      <c r="G54" t="s">
+        <v>211</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
+      </c>
+      <c r="I54" t="s">
+        <v>113</v>
+      </c>
+      <c r="J54" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A55" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" t="s">
+        <v>47</v>
+      </c>
+      <c r="F55" t="s">
+        <v>266</v>
+      </c>
+      <c r="G55" t="s">
+        <v>212</v>
+      </c>
+      <c r="H55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I55" t="s">
+        <v>52</v>
+      </c>
+      <c r="J55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A56" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" t="s">
+        <v>150</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" t="s">
+        <v>265</v>
+      </c>
+      <c r="G56" t="s">
+        <v>213</v>
+      </c>
+      <c r="H56" t="s">
+        <v>51</v>
+      </c>
+      <c r="I56" t="s">
+        <v>52</v>
+      </c>
+      <c r="J56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A57" t="s">
+        <v>214</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" t="s">
+        <v>147</v>
+      </c>
+      <c r="G57" t="s">
+        <v>215</v>
+      </c>
+      <c r="H57" t="s">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s">
+        <v>83</v>
+      </c>
+      <c r="J57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A58" t="s">
+        <v>214</v>
+      </c>
+      <c r="B58" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" t="s">
+        <v>167</v>
+      </c>
+      <c r="F58" t="s">
+        <v>272</v>
+      </c>
+      <c r="G58" t="s">
+        <v>216</v>
+      </c>
+      <c r="H58" t="s">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J58" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A59" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" t="s">
+        <v>266</v>
+      </c>
+      <c r="G59" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" t="s">
+        <v>32</v>
+      </c>
+      <c r="J59" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A60" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" t="s">
+        <v>47</v>
+      </c>
+      <c r="F60" t="s">
+        <v>266</v>
+      </c>
+      <c r="G60" t="s">
+        <v>218</v>
+      </c>
+      <c r="H60" t="s">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s">
+        <v>83</v>
+      </c>
+      <c r="J60" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A61" t="s">
+        <v>214</v>
+      </c>
+      <c r="B61" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" t="s">
+        <v>63</v>
+      </c>
+      <c r="F61" t="s">
+        <v>265</v>
+      </c>
+      <c r="G61" t="s">
+        <v>219</v>
+      </c>
+      <c r="H61" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" t="s">
+        <v>35</v>
+      </c>
+      <c r="J61" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A62" t="s">
+        <v>214</v>
+      </c>
+      <c r="B62" t="s">
+        <v>150</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" t="s">
+        <v>63</v>
+      </c>
+      <c r="F62" t="s">
+        <v>265</v>
+      </c>
+      <c r="G62" t="s">
+        <v>220</v>
+      </c>
+      <c r="H62" t="s">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s">
+        <v>83</v>
+      </c>
+      <c r="J62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A63" t="s">
+        <v>221</v>
+      </c>
+      <c r="B63" t="s">
+        <v>150</v>
+      </c>
+      <c r="C63" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
+        <v>263</v>
+      </c>
+      <c r="G63" t="s">
+        <v>222</v>
+      </c>
+      <c r="H63" t="s">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A64" t="s">
+        <v>223</v>
+      </c>
+      <c r="B64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64" t="s">
+        <v>264</v>
+      </c>
+      <c r="G64" t="s">
+        <v>224</v>
+      </c>
+      <c r="H64" t="s">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s">
+        <v>83</v>
+      </c>
+      <c r="J64" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A65" t="s">
+        <v>223</v>
+      </c>
+      <c r="B65" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G65" t="s">
+        <v>225</v>
+      </c>
+      <c r="H65" t="s">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s">
+        <v>83</v>
+      </c>
+      <c r="J65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A66" t="s">
+        <v>226</v>
+      </c>
+      <c r="B66" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" t="s">
+        <v>43</v>
+      </c>
+      <c r="F66" t="s">
+        <v>145</v>
+      </c>
+      <c r="G66" t="s">
+        <v>227</v>
+      </c>
+      <c r="H66" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" t="s">
+        <v>32</v>
+      </c>
+      <c r="J66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>226</v>
+      </c>
+      <c r="B67" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" t="s">
+        <v>145</v>
+      </c>
+      <c r="G67" t="s">
+        <v>228</v>
+      </c>
+      <c r="H67" t="s">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" t="s">
+        <v>150</v>
+      </c>
+      <c r="C68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" t="s">
+        <v>163</v>
+      </c>
+      <c r="F68" t="s">
+        <v>273</v>
+      </c>
+      <c r="G68" t="s">
+        <v>229</v>
+      </c>
+      <c r="H68" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" t="s">
+        <v>32</v>
+      </c>
+      <c r="J68" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" t="s">
+        <v>163</v>
+      </c>
+      <c r="F69" t="s">
+        <v>273</v>
+      </c>
+      <c r="G69" t="s">
+        <v>230</v>
+      </c>
+      <c r="H69" t="s">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s">
+        <v>83</v>
+      </c>
+      <c r="J69" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F70" t="s">
+        <v>272</v>
+      </c>
+      <c r="G70" t="s">
+        <v>231</v>
+      </c>
+      <c r="H70" t="s">
+        <v>125</v>
+      </c>
+      <c r="I70" t="s">
+        <v>126</v>
+      </c>
+      <c r="J70" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>226</v>
+      </c>
+      <c r="B71" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" t="s">
+        <v>63</v>
+      </c>
+      <c r="F71" t="s">
+        <v>271</v>
+      </c>
+      <c r="G71" t="s">
+        <v>232</v>
+      </c>
+      <c r="H71" t="s">
+        <v>125</v>
+      </c>
+      <c r="I71" t="s">
+        <v>126</v>
+      </c>
+      <c r="J71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="10" customFormat="1">
+      <c r="A72" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="10" customFormat="1">
+      <c r="A73" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" s="10" customFormat="1">
+      <c r="A74" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" s="10" customFormat="1">
+      <c r="A75" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>236</v>
+      </c>
+      <c r="B76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" t="s">
+        <v>263</v>
+      </c>
+      <c r="G76" t="s">
+        <v>237</v>
+      </c>
+      <c r="H76" t="s">
+        <v>70</v>
+      </c>
+      <c r="I76" t="s">
+        <v>71</v>
+      </c>
+      <c r="J76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>236</v>
+      </c>
+      <c r="B77" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" t="s">
+        <v>22</v>
+      </c>
+      <c r="D77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" t="s">
+        <v>153</v>
+      </c>
+      <c r="F77" t="s">
+        <v>264</v>
+      </c>
+      <c r="G77" t="s">
+        <v>238</v>
+      </c>
+      <c r="H77" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" t="s">
+        <v>32</v>
+      </c>
+      <c r="J77" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>236</v>
+      </c>
+      <c r="B78" t="s">
+        <v>150</v>
+      </c>
+      <c r="C78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D78" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" t="s">
+        <v>153</v>
+      </c>
+      <c r="F78" t="s">
+        <v>264</v>
+      </c>
+      <c r="G78" t="s">
+        <v>239</v>
+      </c>
+      <c r="H78" t="s">
+        <v>70</v>
+      </c>
+      <c r="I78" t="s">
+        <v>71</v>
+      </c>
+      <c r="J78" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
+        <v>236</v>
+      </c>
+      <c r="B79" t="s">
+        <v>150</v>
+      </c>
+      <c r="C79" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" t="s">
+        <v>36</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G79" t="s">
+        <v>240</v>
+      </c>
+      <c r="H79" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" t="s">
+        <v>32</v>
+      </c>
+      <c r="J79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>236</v>
+      </c>
+      <c r="B80" t="s">
+        <v>150</v>
+      </c>
+      <c r="C80" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" t="s">
+        <v>36</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G80" t="s">
+        <v>241</v>
+      </c>
+      <c r="H80" t="s">
+        <v>70</v>
+      </c>
+      <c r="I80" t="s">
+        <v>71</v>
+      </c>
+      <c r="J80" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>236</v>
+      </c>
+      <c r="B81" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" t="s">
+        <v>40</v>
+      </c>
+      <c r="F81" t="s">
+        <v>144</v>
+      </c>
+      <c r="G81" t="s">
+        <v>242</v>
+      </c>
+      <c r="H81" t="s">
+        <v>70</v>
+      </c>
+      <c r="I81" t="s">
+        <v>71</v>
+      </c>
+      <c r="J81" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>236</v>
+      </c>
+      <c r="B82" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" t="s">
+        <v>144</v>
+      </c>
+      <c r="G82" t="s">
+        <v>242</v>
+      </c>
+      <c r="H82" t="s">
+        <v>70</v>
+      </c>
+      <c r="I82" t="s">
+        <v>71</v>
+      </c>
+      <c r="J82" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>236</v>
+      </c>
+      <c r="B83" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" t="s">
+        <v>63</v>
+      </c>
+      <c r="F83" t="s">
+        <v>271</v>
+      </c>
+      <c r="G83" t="s">
+        <v>243</v>
+      </c>
+      <c r="H83" t="s">
+        <v>70</v>
+      </c>
+      <c r="I83" t="s">
+        <v>71</v>
+      </c>
+      <c r="J83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>244</v>
+      </c>
+      <c r="B84" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" t="s">
+        <v>145</v>
+      </c>
+      <c r="G84" t="s">
+        <v>245</v>
+      </c>
+      <c r="H84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I84" t="s">
+        <v>71</v>
+      </c>
+      <c r="J84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" t="s">
+        <v>150</v>
+      </c>
+      <c r="C85" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" t="s">
+        <v>163</v>
+      </c>
+      <c r="F85" t="s">
+        <v>273</v>
+      </c>
+      <c r="G85" t="s">
+        <v>246</v>
+      </c>
+      <c r="H85" t="s">
+        <v>70</v>
+      </c>
+      <c r="I85" t="s">
+        <v>71</v>
+      </c>
+      <c r="J85" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" t="s">
+        <v>150</v>
+      </c>
+      <c r="C86" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" t="s">
+        <v>54</v>
+      </c>
+      <c r="F86" t="s">
+        <v>147</v>
+      </c>
+      <c r="G86" t="s">
+        <v>247</v>
+      </c>
+      <c r="H86" t="s">
+        <v>34</v>
+      </c>
+      <c r="I86" t="s">
+        <v>35</v>
+      </c>
+      <c r="J86" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" t="s">
+        <v>54</v>
+      </c>
+      <c r="F87" t="s">
+        <v>147</v>
+      </c>
+      <c r="G87" t="s">
+        <v>248</v>
+      </c>
+      <c r="H87" t="s">
+        <v>70</v>
+      </c>
+      <c r="I87" t="s">
+        <v>71</v>
+      </c>
+      <c r="J87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" t="s">
+        <v>244</v>
+      </c>
+      <c r="B88" t="s">
+        <v>150</v>
+      </c>
+      <c r="C88" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" t="s">
+        <v>167</v>
+      </c>
+      <c r="F88" t="s">
+        <v>272</v>
+      </c>
+      <c r="G88" t="s">
+        <v>249</v>
+      </c>
+      <c r="H88" t="s">
+        <v>34</v>
+      </c>
+      <c r="I88" t="s">
+        <v>35</v>
+      </c>
+      <c r="J88" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" t="s">
+        <v>244</v>
+      </c>
+      <c r="B89" t="s">
+        <v>150</v>
+      </c>
+      <c r="C89" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89" t="s">
+        <v>167</v>
+      </c>
+      <c r="F89" t="s">
+        <v>272</v>
+      </c>
+      <c r="G89" t="s">
+        <v>250</v>
+      </c>
+      <c r="H89" t="s">
+        <v>70</v>
+      </c>
+      <c r="I89" t="s">
+        <v>71</v>
+      </c>
+      <c r="J89" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
+        <v>244</v>
+      </c>
+      <c r="B90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C90" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90" t="s">
+        <v>47</v>
+      </c>
+      <c r="F90" t="s">
+        <v>270</v>
+      </c>
+      <c r="G90" t="s">
+        <v>251</v>
+      </c>
+      <c r="H90" t="s">
+        <v>70</v>
+      </c>
+      <c r="I90" t="s">
+        <v>71</v>
+      </c>
+      <c r="J90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>252</v>
+      </c>
+      <c r="B91" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" t="s">
+        <v>263</v>
+      </c>
+      <c r="G91" t="s">
+        <v>253</v>
+      </c>
+      <c r="H91" t="s">
+        <v>61</v>
+      </c>
+      <c r="I91" t="s">
+        <v>62</v>
+      </c>
+      <c r="J91" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>252</v>
+      </c>
+      <c r="B92" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" t="s">
+        <v>153</v>
+      </c>
+      <c r="F92" t="s">
+        <v>264</v>
+      </c>
+      <c r="G92" t="s">
+        <v>254</v>
+      </c>
+      <c r="H92" t="s">
+        <v>61</v>
+      </c>
+      <c r="I92" t="s">
+        <v>62</v>
+      </c>
+      <c r="J92" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" t="s">
+        <v>252</v>
+      </c>
+      <c r="B93" t="s">
+        <v>150</v>
+      </c>
+      <c r="C93" t="s">
+        <v>22</v>
+      </c>
+      <c r="D93" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93" t="s">
+        <v>36</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G93" t="s">
+        <v>255</v>
+      </c>
+      <c r="H93" t="s">
+        <v>61</v>
+      </c>
+      <c r="I93" t="s">
+        <v>62</v>
+      </c>
+      <c r="J93" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" t="s">
+        <v>252</v>
+      </c>
+      <c r="B94" t="s">
+        <v>150</v>
+      </c>
+      <c r="C94" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" t="s">
+        <v>144</v>
+      </c>
+      <c r="G94" t="s">
+        <v>256</v>
+      </c>
+      <c r="H94" t="s">
+        <v>61</v>
+      </c>
+      <c r="I94" t="s">
+        <v>62</v>
+      </c>
+      <c r="J94" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>252</v>
+      </c>
+      <c r="B95" t="s">
+        <v>150</v>
+      </c>
+      <c r="C95" t="s">
+        <v>22</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" t="s">
+        <v>40</v>
+      </c>
+      <c r="F95" t="s">
+        <v>267</v>
+      </c>
+      <c r="G95" t="s">
+        <v>256</v>
+      </c>
+      <c r="H95" t="s">
+        <v>61</v>
+      </c>
+      <c r="I95" t="s">
+        <v>62</v>
+      </c>
+      <c r="J95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>252</v>
+      </c>
+      <c r="B96" t="s">
+        <v>150</v>
+      </c>
+      <c r="C96" t="s">
+        <v>22</v>
+      </c>
+      <c r="D96" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" t="s">
+        <v>145</v>
+      </c>
+      <c r="G96" t="s">
+        <v>257</v>
+      </c>
+      <c r="H96" t="s">
+        <v>61</v>
+      </c>
+      <c r="I96" t="s">
+        <v>62</v>
+      </c>
+      <c r="J96" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" t="s">
+        <v>252</v>
+      </c>
+      <c r="B97" t="s">
+        <v>150</v>
+      </c>
+      <c r="C97" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97" t="s">
+        <v>163</v>
+      </c>
+      <c r="F97" t="s">
+        <v>273</v>
+      </c>
+      <c r="G97" t="s">
+        <v>258</v>
+      </c>
+      <c r="H97" t="s">
+        <v>61</v>
+      </c>
+      <c r="I97" t="s">
+        <v>62</v>
+      </c>
+      <c r="J97" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" t="s">
+        <v>252</v>
+      </c>
+      <c r="B98" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" t="s">
+        <v>147</v>
+      </c>
+      <c r="G98" t="s">
+        <v>259</v>
+      </c>
+      <c r="H98" t="s">
+        <v>61</v>
+      </c>
+      <c r="I98" t="s">
+        <v>62</v>
+      </c>
+      <c r="J98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" t="s">
+        <v>252</v>
+      </c>
+      <c r="B99" t="s">
+        <v>150</v>
+      </c>
+      <c r="C99" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99" t="s">
+        <v>167</v>
+      </c>
+      <c r="F99" t="s">
+        <v>272</v>
+      </c>
+      <c r="G99" t="s">
+        <v>260</v>
+      </c>
+      <c r="H99" t="s">
+        <v>61</v>
+      </c>
+      <c r="I99" t="s">
+        <v>62</v>
+      </c>
+      <c r="J99" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" t="s">
+        <v>252</v>
+      </c>
+      <c r="B100" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" t="s">
+        <v>47</v>
+      </c>
+      <c r="F100" t="s">
+        <v>268</v>
+      </c>
+      <c r="G100" t="s">
+        <v>261</v>
+      </c>
+      <c r="H100" t="s">
+        <v>61</v>
+      </c>
+      <c r="I100" t="s">
+        <v>62</v>
+      </c>
+      <c r="J100" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>252</v>
+      </c>
+      <c r="B101" t="s">
+        <v>150</v>
+      </c>
+      <c r="C101" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101" t="s">
+        <v>63</v>
+      </c>
+      <c r="F101" t="s">
+        <v>269</v>
+      </c>
+      <c r="G101" t="s">
+        <v>262</v>
+      </c>
+      <c r="H101" t="s">
+        <v>61</v>
+      </c>
+      <c r="I101" t="s">
+        <v>62</v>
+      </c>
+      <c r="J101" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="J2:J401" xr:uid="{BDE5C9B2-005C-4DE0-942D-CF43CE19173B}">
+      <formula1>"ACTIVE,INACTIVE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
+++ b/scripts/teacher-imports/assignments/inputs/teacher-assignments-import-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\assignments\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA2A39B-7624-4954-8E64-91321654C4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC17278A-A997-46EE-8EEB-EF0B6D4B970A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12975" yWindow="2985" windowWidth="15645" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="282">
   <si>
     <t>الحقل</t>
   </si>
@@ -982,7 +982,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAssignmentsImportTable" displayName="TeacherAssignmentsImportTable" ref="A1:J211">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAssignmentsImportTable" displayName="TeacherAssignmentsImportTable" ref="A1:J205">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="بريد المعلم"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="معرّف المدرسة"/>
@@ -1202,18 +1202,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="39" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
@@ -1248,137 +1249,329 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="10" customFormat="1">
-      <c r="A2" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="10" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F5" t="s">
         <v>144</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="10" customFormat="1">
-      <c r="A3" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="10" customFormat="1">
-      <c r="A4" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1">
-      <c r="A5" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" s="10" t="s">
+      <c r="G5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+      <c r="G10" t="s">
+        <v>261</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G11" t="s">
+        <v>262</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="J2:J305" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="J2:J299" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"ACTIVE,INACTIVE"</formula1>
     </dataValidation>
   </dataValidations>
